--- a/excel/baseline_vs_rag_diff.xlsx
+++ b/excel/baseline_vs_rag_diff.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Grâce à ces tests je vois qu'il faut que je m'améliore en mécanique car je n'ai pas du tout compris. J'ai beaucoup d'ignorance car je ne connais pas bien ma leçon. Je me sens plus à l'aise en chimie, mais je confonds encore beaucoup stéréoisomère, énantiomère, de configuration, de conformation . . . J'ai aussi besoin de revoir les titrages car je n'arrive pas à faire les calculs.</t>
+          <t>Il y a eu beaucoup de réponse incorrecte et pas mal d'ignorance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cela révèle que je n’ai pas assez confiance en mes connaissances.</t>
+          <t>Il y a beaucoup de réponses correctes (41) quelques réponses incorrectes (7) et pas d’ignorance.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['MonCal.Facts.RF']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
     </row>
@@ -491,27 +491,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1 réponse dangereuse</t>
+          <t>Cela révèle que je ne suis pas sûr de mes réponses</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>trop d’erreur dangereuse</t>
+          <t>cela révèle que je n’ai pas assez confiance en mes connaissances.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MotOrient.SelfEff']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
     </row>
@@ -521,27 +521,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>je préfère ne pas me risquer à dire que c'est juste si ça peut ne pas l'être</t>
+          <t>Pour espérer davantage au prochain test il va falloir que je révise plus ce qui me permettra d'avoir de l'assurance et de la justesse dans mes réponses</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Je n’ai pas assez revu certain chapitre.</t>
+          <t>Il faudrait que je révise davantage pour le prochain test</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>CTRL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>['CTRL', 'MotOrient.SelfEff']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>CTRL</t>
         </is>
       </c>
     </row>
@@ -551,27 +551,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Beaucoup des sujets je n'avais pas révisé du tout encore</t>
+          <t>Grâce à ces tests je vois qu'il faut que je m'améliore en mécanique car je n'ai pas du tout compris. J'ai beaucoup d'ignorance car je ne connais pas bien ma leçon. Je me sens plus à l'aise en chimie, mais je confonds encore beaucoup stéréoisomère, énantiomère, de configuration, de conformation . . . J'ai aussi besoin de revoir les titrages car je n'arrive pas à faire les calculs.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>J’ai beaucoup de bonnes réponses</t>
+          <t>cela révèle que je n’ai pas assez confiance en mes connaissances.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>DomKldg</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Beaucoup d'erreurs dangereuses</t>
+          <t>Il y a 6 réponses incorrectes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Beaucoup d’erreurs dangereuses (10) mais également beaucoup de savoir certain (27)</t>
+          <t>Il y a beaucoup de réponses correctes (14/20) 5 réponses d’ignorance et 1 réponse incorrecte</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MonCal.Facts.RF']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
     </row>
@@ -611,27 +611,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>je n'étais pas très concentrée</t>
+          <t>1 réponse dangereuse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Je n’étais pas très sûr de moi</t>
+          <t>trop d’erreur dangereuse</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -641,27 +641,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mes connaissances sont encore trop fragiles, je n'ai toujours pas commencé les révisions pour les chapitres (illisible) particulièrement dans le chapitre sur les lois de Newton et la relation entre les acides et les bases.</t>
+          <t>Généralement pas sur de moi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dans les réponses correctes, j’ai beaucoup plus de savoirs certains que de savoir fragile</t>
+          <t>Je ne suis pas sûr de moi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['MotOrient.SelfEff']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
     </row>
@@ -671,27 +671,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Toutefois, cela permet très certainement de cibler les points faibles. Le test est toujours utile.</t>
+          <t>je préfère ne pas me risquer à dire que c'est juste si ça peut ne pas l'être</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dans les courbes obtenues à la suite de mon test, j’ai plutôt un degré de certitude élevé sur les réponses justes et sur les réponses fausses.</t>
+          <t>Je n’ai pas assez revu certain chapitre.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>DomKldg</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MotOrient.Value</t>
+          <t>['MonCal.Interpret']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MotOrient.Value</t>
+          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -701,27 +701,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>un certain nombre de réponses correctes,</t>
+          <t>ce sont des chapitres que je n'ai pas encore bien révisé surtout la chimie.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>J’ai assez de réponse juste, avec un nombre assez correct de savoir certain</t>
+          <t>Je n’ai pas assez revu certain chapitre.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>DomKldg</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>DomKldg</t>
         </is>
       </c>
     </row>
@@ -731,27 +731,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Après avoir relu mes erreurs, j'ai remarqué que ces erreurs provenaient d'une erreur de lecture de la question et rarement d'une réelle erreur / lacune dans mes connaissances.</t>
+          <t>19/32 réponses correctes, peu d'ignorance (2).</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>je reste souvent sur de mes erreurs</t>
+          <t>Il y a beaucoup de réponses correctes (14/20) 5 réponses d’ignorance et 1 réponse incorrecte</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MonCal.Facts.RF']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>je suis relativement déçue</t>
+          <t>Score attribué au fait que je n'étais pas assez attentive et concentrée lors du test.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mais je suis quand même relativement prudent</t>
+          <t>être plus prudent par rapport au test</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BDS.Emotions</t>
+          <t>['StratKldg']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BDS.Emotions</t>
+          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -791,27 +791,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sur la partie mécanique j'ai été plus confiant, à juste titre, alors que dans la partie chimie j'ai été plus prudent (aussi à juste titre)</t>
+          <t>Le diagramme de réponses correctes est proche de la courbe en J, tandis que la courbe des réponses incorrectes ne l'est pas.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Il faut donc que je me fasse plus confiance pour avoir une meilleure courbe J dans les réponses justes.</t>
+          <t>Par rapport aux écarts, ma courbe des réponses correctes forme bien un J mais pas celle des réponses incorrectes.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -821,27 +821,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Je suis aussi surpris de mon score pour la partie chimie</t>
+          <t>Cela révèle que je dois être plus prudente concernant les questions ou je pense avoir faux pour espérer être davantage réaliste</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Le score total est de 23/28,</t>
+          <t>Je pense que je dois être plus prudent lorsque je réponds à une question</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>CTRL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>['MonCal.Interpret', 'CTRL']</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>MonCal.Interpret</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>BDS.Emotions</t>
         </is>
       </c>
     </row>
@@ -851,27 +851,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pour être plus sur de moi il faudrait que je révise plus la chimie pour solidifier mes connaissances.</t>
+          <t>Lors d'un prochain test, je devrais être moins certaine de moi sur les réponses ou j'hésite et être + prudente.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>je ne connaisse pas ma leçon de chimie et que je comprends assez bien la physique.</t>
+          <t>Je pourrais être plus prudent sur ma certitude des réponses pour les prochains tests.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>CTRL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>['CTRL']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>CTRL</t>
         </is>
       </c>
     </row>
@@ -881,27 +881,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>n'ayant absolument pas relu ni réviser la mécanique et même la chimie</t>
+          <t>Beaucoup des sujets je n'avais pas révisé du tout encore</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cela révèle que je n’ai pas assez confiance en mes connaissances.</t>
+          <t>J’ai beaucoup de bonnes réponses</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -911,22 +911,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>uniquement savoir certain ou erreur dangereuse-</t>
+          <t>Beaucoup d'erreurs dangereuses</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>une erreur dangereuse mal lue</t>
+          <t>Beaucoup d’erreurs dangereuses (10) mais également beaucoup de savoir certain (27)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>je n'avais pas révisé presque la totalité de ce qu'il y avait</t>
+          <t>je n'étais pas très concentrée</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cela révèle que je n’ai pas assez confiance en mes connaissances.</t>
+          <t>Je n’étais pas très sûr de moi</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>['BDS.Emotions', 'StratKldg']</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>StratKldg</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>DomKldg</t>
         </is>
       </c>
     </row>
@@ -971,27 +971,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>La plupart de ces erreurs sont dangereuses et les savoirs certains :</t>
+          <t>mes connaissances sont encore trop fragiles, je n'ai toujours pas commencé les révisions pour les chapitres (illisible) particulièrement dans le chapitre sur les lois de Newton et la relation entre les acides et les bases.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Beaucoup d’erreurs dangereuses (10) mais également beaucoup de savoir certain (27)</t>
+          <t>Dans les réponses correctes, j’ai beaucoup plus de savoirs certains que de savoir fragile</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>DomKldg</t>
         </is>
       </c>
     </row>
@@ -1001,27 +1001,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>j'ai plus de réponses correctes en chimie qu'en physique.</t>
+          <t>Je vais tenter de plus travailler pour le prochain test afin d'avoir un meilleur résultat que ceux obtenus cette fois.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>En général, je suis assez sûre de moi concernant mes connaissances en physique-chimie mais en DS j’ai tendance à revenir sur ces certitudes</t>
+          <t>Je pourrais être plus prudent sur ma certitude des réponses pour les prochains tests.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>CTRL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>['CTRL']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>CTRL</t>
         </is>
       </c>
     </row>
@@ -1031,22 +1031,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>La plupart de mes mauvaises réponses sont dans la mécanique, car je n’ai pas appris, ni révisé cette partie avec la loi Kepler</t>
+          <t>Je n'avais pas du tout revu les lois de Kepler et des satellites.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>La majorité de mes réponses sont correctes et dans un savoir certain ce qui est un point satisfaisant</t>
+          <t>Je n’ai pas assez revu certain chapitre.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>DomKldg</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1061,27 +1061,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pour le degré de certitude, c'est dangereux pour les mauvaises réponses, car j’étais plutôt vers une certitude de 100% même si je n'étais pas sûre de mes réponses</t>
+          <t>Toutefois, cela permet très certainement de cibler les points faibles. Le test est toujours utile.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pour être plus réaliste, il faudrait que je sois plus sûr de moi en mettant davantage des certitudes à 100%.</t>
+          <t>Mais les risques pris en savoir certain ont permis une augmentation des points.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>StratKldg</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>['MotOrient.Value']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>MotOrient.Value</t>
         </is>
       </c>
     </row>
@@ -1091,22 +1091,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>j'ai fait plus de fautes que la dernière fois,</t>
+          <t>un certain nombre de réponses correctes,</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mais je peux faire mieux la prochaine fois</t>
+          <t>J’ai assez de réponse juste, avec un nombre assez correct de savoir certain</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>['MonCal.Facts.RF']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Je pense qu'en essayant de relire mes leçons avant le test, je pourrais être plus sûre de mes réponses</t>
+          <t>9 erreurs dangereuses</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dans les courbes obtenues à la suite de mon test, j’ai plutôt un degré de certitude élevé sur les réponses justes et sur les réponses fausses.</t>
+          <t>Résultats : 45 savoirs certains et 3 erreurs dangereuses. 2 erreurs dangereuses</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -1151,27 +1151,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>J'étais globalement moins sûre de moi que lors de la première fois,</t>
+          <t>Après avoir relu mes erreurs, j'ai remarqué que ces erreurs provenaient d'une erreur de lecture de la question et rarement d'une réelle erreur / lacune dans mes connaissances.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Globalement, il y a beaucoup de réponses correctes, (17 sur 24)</t>
+          <t>je reste souvent sur de mes erreurs</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>['MonCal.Facts.DC', 'StratKldg']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>J'étais aussi peu attentive</t>
+          <t>à l'avenir, il faudrait que je prenne plus mon temps pour lire les questions et évaluer réellement mes connaissances et lacunes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>en étant un peu plus prudent.</t>
+          <t>je devrai plus réfléchir sur les questions et mes connaissances</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1196,12 +1196,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['CTRL']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>CTRL</t>
         </is>
       </c>
     </row>
@@ -1211,27 +1211,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Les lois de Kepler sont à apprendre !</t>
+          <t>je suis relativement déçue</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mieux lire les documents</t>
+          <t>Mais je suis quand même relativement prudent</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['BDS.Emotions']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>BDS.Emotions</t>
         </is>
       </c>
     </row>
@@ -1241,27 +1241,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>la majorité de mes fautes n'étaient pas pressenties et mes réponses correctes étaient certaines</t>
+          <t>j'ai eu tendance à faire preuve d'imprudence et à évaluer, à tort, mes réponses comme justes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>La majorité de mes réponses sont correctes et dans un savoir certain ce qui est un point satisfaisant</t>
+          <t>je fais donc preuve d’un peu imprudence.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MonCal.Interpret', 'StratKldg']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
     </row>
@@ -1271,27 +1271,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>J'ai essayé de passer à travers le test rapidement et en ai payé le prix.</t>
+          <t>Sur la partie mécanique j'ai été plus confiant, à juste titre, alors que dans la partie chimie j'ai été plus prudent (aussi à juste titre)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>c’est un gros problème que j’ai depuis très longtemps ! Je voudrais donc finir par dire merci pour ce test, c’était un bon boost de confiance ! :)</t>
+          <t>Il faut donc que je me fasse plus confiance pour avoir une meilleure courbe J dans les réponses justes.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret', 'MotOrient.SelfEff']</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>MotOrient.SelfEff</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>StratKldg</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -1301,27 +1301,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cela me permet de savoir ce que je dois réviser et mes points faibles.</t>
+          <t>Je suis aussi surpris de mon score pour la partie chimie</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>cela révèle que je n’ai pas assez confiance en mes connaissances.</t>
+          <t>Le score total est de 23/28,</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['MonCal.Interpret']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MotOrient.Value</t>
+          <t>BDS.Emotions</t>
         </is>
       </c>
     </row>
@@ -1331,27 +1331,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>le plus grave ? les erreurs dangereuses que j'ai fait.</t>
+          <t>Pour être plus sur de moi il faudrait que je révise plus la chimie pour solidifier mes connaissances.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>je pensais être sur des résultats pour lesquels j’ai eu erreur dangereuse</t>
+          <t>je ne connaisse pas ma leçon de chimie et que je comprends assez bien la physique.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>DomKldg</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['DomKldg', 'CTRL']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>DomKldg</t>
         </is>
       </c>
     </row>
@@ -1361,27 +1361,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ce test m'a permis de réaliser que mes connaissances sont moins solides que ce que j'espérais</t>
+          <t>Par rapport à la dernière fois j'ai fait moins d'erreurs d'inattention car j'ai bien vérifié même les questions que j'ai eu juste.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>c’est un gros problème que j’ai depuis très longtemps ! Je voudrais donc finir par dire merci pour ce test, c’était un bon boost de confiance ! :)</t>
+          <t>J’ai fait des erreurs d’inattention, sans vraiment réfléchir à toutes les questions.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>StratKldg</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>['StratKldg']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MotOrient.Value</t>
+          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -1391,27 +1391,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Il faut donc que je révise les formules / équations de Kepler, Newton, et de l'accélération et pour la chimie : la nomenclature, la géométries des molécules et les acides/bases.</t>
+          <t>il y a une majorité de réponses vraies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Les 4 mauvaises réponses sont sur les formules (3) et une sur le ph.</t>
+          <t>Il y a une majorité de réponses correctes</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>['MonCal.Facts.RF']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>beaucoup d'erreurs dangereuses (10)</t>
+          <t>le nombre de erreurs dangereuses a diminué</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Beaucoup d’erreurs dangereuses (10) mais également beaucoup de savoir certain (27)</t>
+          <t>Mon nombre d’erreurs dangereuses est bien au-dessus de la courbe en J</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>La courbe en J des réponses correctes montre qu'en général, je sais quand j'ai la bonne réponse. Cependant je ne sais pas forcément quand j'ai la mauvaise réponse, la courbe en J des réponses incorrectes m'indiquant beaucoup d'erreurs dangereuses et ne suivant pas la forme du J. Cela relève d'une certaine imprudence.</t>
+          <t>n'ayant absolument pas relu ni réviser la mécanique et même la chimie</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>La courbe d’erreur ne forme pas un J contrairement à la courbe de bonnes réponses</t>
+          <t>cela révèle que je n’ai pas assez confiance en mes connaissances.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>DomKldg</t>
         </is>
       </c>
     </row>
@@ -1481,27 +1481,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Il faut que je révise la chimie, car mes connaissances sont floues et donc la certitude de mes réponses est affectée.</t>
+          <t>Il y a aussi comme la dernière fois des erreurs d'inattention.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cela révèle que je n’ai pas assez confiance en mes connaissances.</t>
+          <t>J’ai fait des erreurs d’inattention, sans vraiment réfléchir à toutes les questions.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>StratKldg</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['StratKldg']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>presque autant d'erreurs dangereuses que de présumé, mais aussi autant de savoir fragile que de certain.</t>
+          <t>uniquement savoir certain ou erreur dangereuse-</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Il faudrait que j’aie plus de réponses en erreur présumée et savoir fragile pour éviter les erreurs dangereuses.</t>
+          <t>une erreur dangereuse mal lue</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>je suis sûr dans toutes mes réponses où je crois avoir raison, ce qui me donne uniquement des savoirs certains et des erreurs dangereuses. Ma courbe de bonnes réponses est en J mais l'autre est en J inversé (en L en fait).</t>
+          <t>je n'avais pas révisé presque la totalité de ce qu'il y avait</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>je pense que j’aurai pu être plus sûr de mes réponses correctes et éviter les erreurs dangereuses.</t>
+          <t>cela révèle que je n’ai pas assez confiance en mes connaissances.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>DomKldg</t>
         </is>
       </c>
     </row>
@@ -1571,27 +1571,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Globalement, j'ai réussi à être plus certaine de mes réponses (22 savoirs certains et 1 savoir fragile) mais ça a créé de ce fait quelques erreurs dangereuses (7). Par rapport au premier test, je peux remarquer que la courbe en J est plus conséquente pour les réponses correctes</t>
+          <t>Globalement il y a plus ou moins autant de réponses correctes et incorrectes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Il faudrait que j’aie plus de réponses en erreur présumée et savoir fragile pour éviter les erreurs dangereuses.</t>
+          <t>Globalement, il y a plus de réponses correctes que de réponses incorrectes, et aucune ignorance.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MonCal.Facts.RF']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
     </row>
@@ -1601,27 +1601,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Il y a un manque de rigueur car j'ai mal lu les énoncés et cela m'a induit en erreur et c'est pour cela que j'ai eu des réponses qui étaient erronées</t>
+          <t>La plupart de ces erreurs sont dangereuses et les savoirs certains :</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pour la prochaine fois, il faudrait que je prenne un peu plus de recul pour éviter les erreurs d’étourderie</t>
+          <t>Beaucoup d’erreurs dangereuses (10) mais également beaucoup de savoir certain (27)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -1631,27 +1631,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C'est un peu meilleur que le premier test mais c'est parce que les questions étaient sur des chapitres vus en Terminale tandis que le premier test était sur des chapitres vus en Première.</t>
+          <t>je devrais peut-être être un peu plus prudent</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>c’est un gros problème que j’ai depuis très longtemps ! Je voudrais donc finir par dire merci pour ce test, c’était un bon boost de confiance ! :)</t>
+          <t>en étant un peu plus prudent.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>CTRL</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['CTRL']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
     </row>
@@ -1661,27 +1661,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>On peut dire que j'ai eu ce score car je ne révise jamais sauf la veille ou le jour même d'un contrôle, j'aurais sûrement un meilleur score en révisant régulièrement</t>
+          <t>j'ai plus de réponses correctes en chimie qu'en physique.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ce score provient d’oublis de connaissance de manques de connaissance.</t>
+          <t>En général, je suis assez sûre de moi concernant mes connaissances en physique-chimie mais en DS j’ai tendance à revenir sur ces certitudes</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>DomKldg</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>CTRL</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -1691,27 +1691,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Beaucoup de savoir certain avec 5 erreurs dangereuses.</t>
+          <t>J'ai plus confiance en mes résultats par rapport à la dernière fois</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Beaucoup d’erreurs dangereuses (10) mais également beaucoup de savoir certain (27)</t>
+          <t>De plus, je pense aussi avoir été trop confiante dans mes résultats.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MotOrient.SelfEff']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>J'ai mal jugé mes réponses et surestimé mes compétences</t>
+          <t>j'ai beaucoup d'erreurs dangereuses</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mes erreurs : j’en ai 3 (2 dangereuses 1 résumée). Mes réponses justes : 14 dont 10 savoirs certains et 4 fragiles</t>
+          <t>j’ai aussi fait beaucoup d’erreurs dangereuse</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -1751,27 +1751,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ce test m'a permis de comprendre que je dois faire plus attention aux énoncés.</t>
+          <t>Je manque aussi de vocabulaire</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Le test était instructif et a permis de revoir l’ensemble du programme, il m’a été très profitable.</t>
+          <t>je manque de connaissances</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MotOrient.Value</t>
+          <t>DomKldg</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MotOrient.Value</t>
+          <t>DomKldg</t>
         </is>
       </c>
     </row>
@@ -1781,27 +1781,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6 erreurs dangereuses, 3 présumées, 4 ignorances déclarée, 3 savoir fragile, 16 savoir certain</t>
+          <t>ce test est très réaliste/ précis.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1 erreur dangereuse, 3 erreurs présumées, 3 ignorances déclarées, 3 savoir fragile et 18 savoir certains</t>
+          <t>Le test est utile pour savoir quoi revoir.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MotOrient.Value</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MotOrient.Value']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MotOrient.Value</t>
         </is>
       </c>
     </row>
@@ -1811,27 +1811,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Relativement satisfait car peu d'erreurs et peu savoir fragile comme je le pensais lors du test. J'étais assez souvent très sûr de moi.</t>
+          <t>La plupart de mes mauvaises réponses sont dans la mécanique, car je n’ai pas appris, ni révisé cette partie avec la loi Kepler</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Il faudrait que j’aie plus de réponses en erreur présumée et savoir fragile pour éviter les erreurs dangereuses.</t>
+          <t>La majorité de mes réponses sont correctes et dans un savoir certain ce qui est un point satisfaisant</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>DomKldg</t>
         </is>
       </c>
     </row>
@@ -1841,27 +1841,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>j'ai tendance à être trop sûre de moi.</t>
+          <t>ce qui concerne les mauvaises réponses, c'est une mauvaise compréhension des questions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Question après question, j’étais plutôt sûre de moi.</t>
+          <t>surement dû à une mauvaise compréhension de cette partie du cours</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>DomKldg</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>J'ai aussi appris que je suis incapable de me concentrer devant un écran d'ordinateur, je vais trop vite du coup je comprends mal les énoncés et les questions</t>
+          <t>Pour le degré de certitude, c'est dangereux pour les mauvaises réponses, car j’étais plutôt vers une certitude de 100% même si je n'étais pas sûre de mes réponses</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>je devrai plus réfléchir sur les questions et mes connaissances</t>
+          <t>Pour être plus réaliste, il faudrait que je sois plus sûr de moi en mettant davantage des certitudes à 100%.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MonCal.Interpret', 'DomKldg']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Je dois mieux lire les énoncés et être plus attentif sur les réponses</t>
+          <t>j'ai essayé d'avoir confiance en moi.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>j’ai donc tendance a être trop confiant sur des réponses fausses et pas assez sur des réponses exacts.</t>
+          <t>Il faut que j’aie un peu plus confiance en moi.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MotOrient.SelfEff']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
     </row>
@@ -1931,27 +1931,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>23 réponses correctes, soit 71% de réponses justes et 9 incorrectes)</t>
+          <t>J'ai quand même beaucoup d'erreurs dangereuses (6 au total). J'ai 2 ignorance déclarée, ce qui est relativement peu. Dans mes réponses correctes, j'ai plus de savoir fragile que de savoir certain.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ma courbe de réponses correctes augment bien, et pour ce qui est de ma courbe de réponses incorrectes, elle doit avoir plus de d’erreurs présumées à 60%</t>
+          <t>J’ai 2 réponses incorrectes qui sont toutes les 2 des réponses dangereuses. J’ai plus de savoir certain que fragile (18&gt;4).</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -1961,27 +1961,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>des connaissances certaines dans le domaine de la physique chimie</t>
+          <t>je suis assez prudent</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>à part peut-être pour certains concepts de la chimie.</t>
+          <t>je suis trop prudent</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MonCal.Interpret']</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
     </row>
@@ -1991,27 +1991,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>je pense être plutôt réaliste et ne pas avoir besoin de devenir beaucoup plus réaliste</t>
+          <t>j'ai fait plus de fautes que la dernière fois,</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Je pense donc que pour être plus réaliste, je devrais me faire plus confiance,</t>
+          <t>Mais je peux faire mieux la prochaine fois</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>['MonCal.Facts.RF']</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
     </row>
@@ -2021,27 +2021,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ce test ne m'apporte pas grand-chose, que quelques connaissances sur quelques détails précis</t>
+          <t>Je n'avais pas révisé mes leçons</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pour le prochain test, il faut moins de doutes sur les choses connues.</t>
+          <t>Je n’ai pas assez revu certain chapitre.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>DomKldg</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MotOrient.Value</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MotOrient.Value</t>
+          <t>DomKldg</t>
         </is>
       </c>
     </row>
@@ -2051,22 +2051,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ces erreurs dangereuses sont dues à un manque de connaissances.</t>
+          <t>D'après ma courbe, j'ai tendance à être à la fois trop prudente (avec 12 savoirs fragiles) et à la fois pas assez (7 erreurs dangereuses)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mes erreurs dangereuses sont surtout dues a des petites erreurs d’étourderie.</t>
+          <t>Sur les courbes J, j’ai plus d’erreurs dangereuses et de savoirs fragiles.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MonCal.Facts.DC', 'MonCal.Interpret']</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>La prochaine fois, je ferais attention aux tournures des phrases qui peuvent être dangereuses.</t>
+          <t>Je pense qu'en essayant de relire mes leçons avant le test, je pourrais être plus sûre de mes réponses</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>J’ai fait tout de même 5 erreurs dangereuses</t>
+          <t>Dans les courbes obtenues à la suite de mon test, j’ai plutôt un degré de certitude élevé sur les réponses justes et sur les réponses fausses.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>['MotOrient.SelfEff', 'CTRL']</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>sachant que je n'étais pas là pour la leçon de géométrie moléculaire et que je n'ai pas très bien compris</t>
+          <t>J'étais globalement moins sûre de moi que lors de la première fois,</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>J’étais globalement assez cohérente dans mon degré de certitude et la justesse de mes réponses</t>
+          <t>Question après question, j’étais plutôt sûre de moi.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['MotOrient.SelfEff']</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
     </row>
@@ -2141,27 +2141,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>quelques difficultés en chimie.</t>
+          <t>J'étais aussi peu attentive</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>quelques réponses faibles.</t>
+          <t>en étant un peu plus prudent.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>CTRL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['StratKldg']</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -2171,27 +2171,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>il faut revoir certaines choses de mon cours</t>
+          <t>Les lois de Kepler sont à apprendre !</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>J’ai plutôt pas mal de savoir certain</t>
+          <t>mieux lire les documents</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>CTRL</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>DomKldg</t>
         </is>
       </c>
     </row>
@@ -2201,27 +2201,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>J'ai eu tout juste en physique, mais j'ai plus de mal en chimie car c'est moins concret. Les formules sont dures à comprendre donc à apprendre. De plus, mes erreurs dangereuses en chimie montrent que je n'ai pas tout compris.</t>
+          <t>la majorité de mes fautes n'étaient pas pressenties et mes réponses correctes étaient certaines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>J’ai eu beaucoup (~) de erreurs dangereuses mais en tout pas mal de réponse juste</t>
+          <t>La majorité de mes réponses sont correctes et dans un savoir certain ce qui est un point satisfaisant</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bon test permettant ainsi de connaitre la qualité des connaissances.</t>
+          <t>J'ai essayé de passer à travers le test rapidement et en ai payé le prix.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Globalement, le test m’a donné de la confiance dans mes connaissances</t>
+          <t>c’est un gros problème que j’ai depuis très longtemps ! Je voudrais donc finir par dire merci pour ce test, c’était un bon boost de confiance ! :)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MotOrient.Value</t>
+          <t>['StratKldg']</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MotOrient.Value</t>
+          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -2261,27 +2261,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6 erreurs dangereuses, 18 savoirs certains et 4 savoir fragiles, 1 erreur présumée.</t>
+          <t>Cela me permet de savoir ce que je dois réviser et mes points faibles.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1 erreur dangereuse, 3 erreurs présumées, 3 ignorances déclarées, 3 savoir fragile et 18 savoir certains</t>
+          <t>cela révèle que je n’ai pas assez confiance en mes connaissances.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MotOrient.Value']</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MotOrient.Value</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Les erreurs dangereuses viennent du fait que je lis parfois trop vite et de ce fait j'oublie des informations</t>
+          <t>le plus grave ? les erreurs dangereuses que j'ai fait.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Et un peu trop d’erreurs dangereuses</t>
+          <t>je pensais être sur des résultats pour lesquels j’ai eu erreur dangereuse</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
     </row>
@@ -2321,27 +2321,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4 erreurs dangereuses et 6 erreurs présumées et 4 savoir fragile ainsi que 18 savoir certain</t>
+          <t>La mécanique est un thème difficile et je suis dans l'ensemble trop sûre de moi en mécanique.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1 erreur dangereuse, 3 erreurs présumées, 3 ignorances déclarées, 3 savoir fragile et 18 savoir certains</t>
+          <t xml:space="preserve">Dans l’ensemble je suis très voire trop sûr de moi </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MotOrient.SelfEff']</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
     </row>
@@ -2351,27 +2351,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Certaines de ces erreurs sont dues à un manque de réflexion par rapport aux questions (ex: confondre semi-équation et équation de réaction)</t>
+          <t>Ce test m'a permis de réaliser que mes connaissances sont moins solides que ce que j'espérais</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>C’est quand même intéressant de voir sur quelles questions on a fait une erreur dangereuse car je me suis rendu compte que je faisais quelques erreurs bêtes. *</t>
+          <t>c’est un gros problème que j’ai depuis très longtemps ! Je voudrais donc finir par dire merci pour ce test, c’était un bon boost de confiance ! :)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MotOrient.Value</t>
         </is>
       </c>
     </row>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mes fautes sont surtout en chimie, c'est tout à fait normal car je ne comprends pas trop certaines méthodes à faire</t>
+          <t>J'ai autant de réponses incorrectes que d'ignorances.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>J’ai fait des erreurs d’inattention, sans vraiment réfléchir à toutes les questions.</t>
+          <t>Globalement j’ai beaucoup de réponses correctes, peu de réponses incorrectes et peu d’ignorances.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['MonCal.Facts.RF']</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
     </row>
@@ -2411,22 +2411,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>beaucoup trop d'erreur dangereuses mais une courbe de savoir certain plutôt bonne</t>
+          <t>avec 5 savoir fragile et 15 savoir certain</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Et un peu trop d’erreurs dangereuses</t>
+          <t>J’ai 20 savoir certains et 15 savoir fragile</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2441,27 +2441,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Il faut que je travaille mieux mes notions</t>
+          <t>c'est bien de voir que la plupart du temps je suis certaine quand j'ai raison</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Il me faut mieux connaitre mon cours plus tard.</t>
+          <t>Je pense que je suis sûre de moi pour la plupart des questions</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>['MotOrient.SelfEff']</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
     </row>
@@ -2471,27 +2471,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>L'objectif est donc une attention plus marquée dans la lecture des questions</t>
+          <t>9 réponses fausses (4 ! 5. . )3 ignorances20 réponses correctes (8 . . . 12 :)23/32</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>J’observe une bonne certitude sur une majorité des questions</t>
+          <t>(17/24)5 réponses fausses3 ignorance16 réponses correctes</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MonCal.Facts.RF']</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
     </row>
@@ -2501,27 +2501,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Les courbes en J ne sont pas cohérentes, au niveau des réponses incorrectes : bcp de réponses dangereuses à 100% ou 90% de certitude.</t>
+          <t>je ne suis pas du tout sûr de ce que je réponds en chimie</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Globalement, il y a quelques erreurs dangereuses (3) et présumées (3) et une majorité de réponses correctes. La courbe ne J atteint son maximum dans les réponses correctes pour 80%.</t>
+          <t>Je ne suis pas sûr de moi</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MotOrient.SelfEff', 'DomKldg']</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
     </row>
@@ -2531,27 +2531,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>trois erreurs dangereuses (à80%) qui sont dues à une mauvaise lecture de l'énoncé et une confusion entre plusieurs éléments de la consigne</t>
+          <t>Il faut donc que je révise les formules / équations de Kepler, Newton, et de l'accélération et pour la chimie : la nomenclature, la géométries des molécules et les acides/bases.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Globalement, il y a quelques erreurs dangereuses (3) et présumées (3) et une majorité de réponses correctes. La courbe ne J atteint son maximum dans les réponses correctes pour 80%.</t>
+          <t>Les 4 mauvaises réponses sont sur les formules (3) et une sur le ph.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>DomKldg</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>DomKldg</t>
         </is>
       </c>
     </row>
@@ -2561,27 +2561,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ce qui témoigne d'une bonne connaissance d'une partie du programme et une connaissance partielle d'une autre partie du programme</t>
+          <t>Il y a la moitié de réponses correctes et l'autre moitié incorrecte.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>On peut constater un manque de confiance concernant les connaissances acquises et comprises.</t>
+          <t>J’ai obtenu deux réponses incorrectes et dix-huit réponses correctes</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['MonCal.Facts.RF']</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
     </row>
@@ -2591,27 +2591,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>j'ai souvent répondu trop vite</t>
+          <t>beaucoup d'erreurs dangereuses (10)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>je semble encore trop confiant</t>
+          <t>Beaucoup d’erreurs dangereuses (10) mais également beaucoup de savoir certain (27)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -2621,27 +2621,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>je n'avais pas de connaissance spécifique sur ce cours (mots spécifiques scientifiques)</t>
+          <t>La courbe en J des réponses correctes montre qu'en général, je sais quand j'ai la bonne réponse. Cependant je ne sais pas forcément quand j'ai la mauvaise réponse, la courbe en J des réponses incorrectes m'indiquant beaucoup d'erreurs dangereuses et ne suivant pas la forme du J. Cela relève d'une certaine imprudence.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>il faudrait que je sois bien plus rigoureux sur les connaissances de cours</t>
+          <t>La courbe d’erreur ne forme pas un J contrairement à la courbe de bonnes réponses</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['MonCal.Interpret', 'MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
     </row>
@@ -2651,27 +2651,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>j'ai été beaucoup moins prudente que sur le dernier test, j'ai pris des risques</t>
+          <t>Pour espérer devenir davantage réaliste lors du prochain test, je pourrais me fier davantage à mes réelles connaissances plutôt qu'à mes estimations sur quelle réponse pourrait être la bonne, si une question semble une question piège,</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Même si lors du test, j’ai malheureusement échangé les réponses de certaines questions (donc deux erreurs dangereuses pour rien) et d’autres étaient ambigües.</t>
+          <t>Je pourrais devenir davantage réaliste lors de prochain test en acquérant (!) plus de connaissance.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>CTRL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>['CTRL', 'MotOrient.SelfEff']</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>CTRL</t>
         </is>
       </c>
     </row>
@@ -2681,27 +2681,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>9 savoir certain 4 fragile 4 erreurs présumées et 3 dangereuses.</t>
+          <t>Il faut que je révise la chimie, car mes connaissances sont floues et donc la certitude de mes réponses est affectée.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1 erreur dangereuse, 3 erreurs présumées, 3 ignorances déclarées, 3 savoir fragile et 18 savoir certains</t>
+          <t>cela révèle que je n’ai pas assez confiance en mes connaissances.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>DomKldg</t>
         </is>
       </c>
     </row>
@@ -2711,27 +2711,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>mes erreurs viennent majoritairement du fait que je ne comprends absolument pas le chapitre de chimie sur lequel nous avons eu des questions (solution titrante/titrée, ph, pka)</t>
+          <t>Il faut que je regarde les questions de plus près car la formulation peut être trompeuse à certains moments.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>J’observe une bonne certitude sur une majorité des questions</t>
+          <t>Il faut donc que je prenne plus de temps pour répondre &amp; lire les questions la prochaine fois.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>CTRL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['CTRL']</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>StratKldg</t>
         </is>
       </c>
     </row>
@@ -2741,27 +2741,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>j'ai fait beaucoup d'erreurs présumées</t>
+          <t>Le test m'a permis de me donner de la confiance dans mes connaissances et mon savoir.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>j’ai fait beaucoup d’erreurs</t>
+          <t>Globalement, le test m’a donné de la confiance dans mes connaissances</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MotOrient.SelfEff']</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
     </row>
@@ -2771,27 +2771,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>j'ai échangé 2 valeurs dans une formule que je n'ai pas trop comprise</t>
+          <t>je fais beaucoup d'erreurs dangereuses en chimie.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dans l’ensemble je suis très voire trop sûr de moi </t>
+          <t>j’ai aussi fait beaucoup d’erreurs dangereuse</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -2801,27 +2801,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>j’ai des fois mal lu les consignes</t>
+          <t>trop prudent</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>j’ai un manque de connaissances.</t>
+          <t>Trop prudent</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MonCal.Interpret']</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Interpret</t>
         </is>
       </c>
     </row>
@@ -2831,27 +2831,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>J’aurais mieux réussis si j’avais pu poser les questions à l'écrit sur une feuille et si j'avais pour prendre mon temps en recontextualisant les questions qui ont déjà été vues en classes ou évaluation.</t>
+          <t>presque autant d'erreurs dangereuses que de présumé, mais aussi autant de savoir fragile que de certain.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pour la plupart des questions, j’ai plutôt bien réussi à dire si j’allais avoir juste ou non</t>
+          <t>Il faudrait que j’aie plus de réponses en erreur présumée et savoir fragile pour éviter les erreurs dangereuses.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>StratKldg</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -2861,27 +2861,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>je n'ai pas pris le temps de bien comprendre les énoncés</t>
+          <t>Il y a globalement beaucoup de réponses correctes</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pour la prochaine je pourrais prendre plus mon temps</t>
+          <t>Globalement, il y a beaucoup de réponses correctes, (17 sur 24)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MonCal.Facts.RF']</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.RF</t>
         </is>
       </c>
     </row>
@@ -2891,27 +2891,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>dans certaines questions je n’étais pas concentré sur le sujet</t>
+          <t>je suis sûr dans toutes mes réponses où je crois avoir raison, ce qui me donne uniquement des savoirs certains et des erreurs dangereuses. Ma courbe de bonnes réponses est en J mais l'autre est en J inversé (en L en fait).</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Je pense ne pas être assez sûr de moi pour certaines questions</t>
+          <t>La courbe de bonnes réponses correspond à la courbe en J mais pas celle des erreurs qui est légèrement inversée.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MonCal.Facts.DC', 'MotOrient.SelfEff']</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -2921,27 +2921,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Incompréhension acide/base + titrage</t>
+          <t>Globalement, j'ai réussi à être plus certaine de mes réponses (22 savoirs certains et 1 savoir fragile) mais ça a créé de ce fait quelques erreurs dangereuses (7). Par rapport au premier test, je peux remarquer que la courbe en J est plus conséquente pour les réponses correctes</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Réponses incorrectes : 4ignorances : 7réponses correctes</t>
+          <t>Il faudrait que j’aie plus de réponses en erreur présumée et savoir fragile pour éviter les erreurs dangereuses.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>MonCal.Facts.RF</t>
+          <t>StratKldg</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -2951,27 +2951,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ceci démontre de mon évolution sur le plan mental notamment. Dans mon assurance à répondre aux questions.</t>
+          <t>Pour le prochain test, il faudrait que je me laisse un peu plus de temps avant de répondre et bien analyser les docs.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>J’ai fait des erreurs d’inattention, sans vraiment réfléchir à toutes les questions.</t>
+          <t>Je pourrais être plus prudent sur ma certitude des réponses pour les prochains tests.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>CTRL</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>['CTRL']</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MotOrient.SelfEff</t>
+          <t>CTRL</t>
         </is>
       </c>
     </row>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>mon problème réside dans ma précipitation</t>
+          <t>Il y a un manque de rigueur car j'ai mal lu les énoncés et cela m'a induit en erreur et c'est pour cela que j'ai eu des réponses qui étaient erronées</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>J’espère devenir réaliste en prenant plus mon temps</t>
+          <t>Pour la prochaine fois, il faudrait que je prenne un peu plus de recul pour éviter les erreurs d’étourderie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['StratKldg']</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4 dangereuses et 5 présumées</t>
+          <t>5 : erreurs dangereuses, 6 erreurs présumées, 11 savoirs fragiles, 10 savoir certains :</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Résultats : 45 savoirs certains et 3 erreurs dangereuses. 2 erreurs dangereuses</t>
+          <t>32 savoirs certains, 2 savoirs fragiles, 7 erreurs présumées, 4 erreurs dangereuses, 3 ignorance déclarée-</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3041,27 +3041,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>J'ai répondu trop vite aux questions. je n'ai pas assez réfléchi à certaines questions.</t>
+          <t>C'est un peu meilleur que le premier test mais c'est parce que les questions étaient sur des chapitres vus en Terminale tandis que le premier test était sur des chapitres vus en Première.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>je devrai plus réfléchir sur les questions et mes connaissances</t>
+          <t>c’est un gros problème que j’ai depuis très longtemps ! Je voudrais donc finir par dire merci pour ce test, c’était un bon boost de confiance ! :)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>MotOrient.SelfEff</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['DomKldg']</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>DomKldg</t>
         </is>
       </c>
     </row>
@@ -3071,27 +3071,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>un manque d'attention sur certains détails</t>
+          <t>Il y a pas mal de savoir certain et environ 1/3 d'erreurs dangereuses</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>d’un manque de connaissances sur certains points</t>
+          <t>Je vois qu’il y a qu’une ignorance ce qui est pas mal, après il y a 7 erreurs dangereuses</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -3101,22 +3101,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Des erreurs que je pouvait éviter souvent dû au manque de concentration</t>
+          <t>On peut dire que j'ai eu ce score car je ne révise jamais sauf la veille ou le jour même d'un contrôle, j'aurais sûrement un meilleur score en révisant régulièrement</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>on peut penser que je suis assez prudent</t>
+          <t>Ce score provient d’oublis de connaissance de manques de connaissance.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>DomKldg</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>['StratKldg', 'CTRL']</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>mauvais apprentissage du cours</t>
+          <t>Beaucoup de savoir certain avec 5 erreurs dangereuses.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>en apprenant mieux en cours,</t>
+          <t>Beaucoup d’erreurs dangereuses (10) mais également beaucoup de savoir certain (27)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>CTRL</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>DomKldg</t>
+          <t>['MonCal.Facts.DC']</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>StratKldg</t>
+          <t>MonCal.Facts.DC</t>
         </is>
       </c>
     </row>
@@ -3161,27 +3161,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>bcp d'erreurs dangereuses</t>
+          <t>Pour le prochain test, je devrais approfondir les bases du cours (non-acquis) avec des exercices.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cependant trop d’erreurs dangereuses (7/40)</t>
+          <t>Je pourrais être plus prudent sur ma certitude des réponses pour les prochains tests.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>MonCal.Interpret</t>
+          <t>CTRL</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>['CTRL']</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MonCal.Facts.DC</t>
+          <t>CTRL</t>
         </is>
       </c>
     </row>
@@ -3191,27 +3191,4317 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
+          <t>J'ai mal jugé mes réponses et surestimé mes compétences</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Mes erreurs : j’en ai 3 (2 dangereuses 1 résumée). Mes réponses justes : 14 dont 10 savoirs certains et 4 fragiles</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Ce test m'a permis de comprendre que je dois faire plus attention aux énoncés.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Le test était instructif et a permis de revoir l’ensemble du programme, il m’a été très profitable.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>6 erreurs dangereuses, 3 présumées, 4 ignorances déclarée, 3 savoir fragile, 16 savoir certain</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1 erreur dangereuse, 3 erreurs présumées, 3 ignorances déclarées, 3 savoir fragile et 18 savoir certains</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Relativement satisfait car peu d'erreurs et peu savoir fragile comme je le pensais lors du test. J'étais assez souvent très sûr de moi.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Il faudrait que j’aie plus de réponses en erreur présumée et savoir fragile pour éviter les erreurs dangereuses.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret', 'BDS.Emotions']</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5 réponse dangereuse, 1 erreur présumée, 5 ignorance déclarée, 6 savoir fragile et 15 certain</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1 erreur dangereuse, 3 erreurs présumées, 3 ignorances déclarées, 3 savoir fragile et 18 savoir certains</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Globalement, il y a plus de réponses savoir certain que d'erreur dangereuse ,</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Il y a globalement des réponses correctes même si beaucoup sont incertaines, et une seule erreur dangereuse</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>e trouve que j'ai été trop rapide dans mes choix de réponse ainsi à l'avenir il me faudra être plus réfléchi. Aussi des petites révisions ne me feraient pas de mal.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>plus réfléchir avant de répondre, aller moins vite, bien vérifier mes réponses.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Je pense que je peux m'améliorer en étant plus prudente et en faisant plus attention aux énoncés.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>en étant un peu plus prudent.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Cela Vient en parti du fait que je ne connaissais pas les formules du cours et d'interprétations fausses des documents</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>J’aurais dû mieux apprendre mes cours et certaines fois être plus attentive aux documents car j’ai fait deux erreurs de lecture que j’aurais surement pu éviter</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Les courbes ne sont pas en J (légèrement pour les bonnes réponses, mais pas du tout sur les mauvaises)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Les courbes en J sont plutôt écrasées</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>j'ai tendance à être trop sûre de moi.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Question après question, j’étais plutôt sûre de moi.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>J'ai plutôt assez bien réussi le test, mieux que le premier il me semble</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Mon test est plutôt réussi</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Mon savoir est là, mais cependant je fais encore trop d'erreurs d'inattention sur des choses bêtes. Il faut que je me concentre tout le long pour répondre à toutes les questions.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>J’ai fait des erreurs d’inattention, sans vraiment réfléchir à toutes les questions.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>['StratKldg', 'CTRL']</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Je suis assez content du résultat, ça aurait pu être pire. Ce test provoque chez moi de l'anxiété</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Je suis assez contente du résultat</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>['BDS.Emotions']</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Cela révèle mon énorme manque de confiance en moi</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Cela révèle de trop de confiance sur certaine de mes réponses</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>['MotOrient.SelfEff']</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>J'ai aussi appris que je suis incapable de me concentrer devant un écran d'ordinateur, je vais trop vite du coup je comprends mal les énoncés et les questions</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>je devrai plus réfléchir sur les questions et mes connaissances</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>['StratKldg', 'CTRL']</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Globalement, il y a beaucoup de réponses certaines mais aussi beaucoup d'erreurs dangereuses.</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>j’ai aussi fait beaucoup d’erreurs dangereuse</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Je suis toujours trop sûr de mes réponses</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>je suis trop sûr de moi</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>['MotOrient.SelfEff']</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Je dois mieux lire les énoncés et être plus attentif sur les réponses</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>j’ai donc tendance a être trop confiant sur des réponses fausses et pas assez sur des réponses exacts.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Pour m'améliorer, je pourrais donc prendre plus de temps pour répondre et assimiler les énoncés.</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Il faut donc prendre son temps et vérifier même si on est sûr de la réponse.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>23 réponses correctes, soit 71% de réponses justes et 9 incorrectes)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ma courbe de réponses correctes augment bien, et pour ce qui est de ma courbe de réponses incorrectes, elle doit avoir plus de d’erreurs présumées à 60%</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>des connaissances certaines dans le domaine de la physique chimie</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>à part peut-être pour certains concepts de la chimie.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>mes 7 erreurs dangereuses peuvent relever une certaine imprudence</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>j’ai pas mal d’erreurs dangereuses -&gt; imprudence</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Afin de devenir davantage réaliste lors du prochain test, il me faudra être plus technique dans mes connaissances en physique chimie.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Je pourrais devenir davantage réaliste lors de prochain test en acquérant (!) plus de connaissance.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Beaucoup de réponses correctes</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Beaucoup de réponses correctes</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Les courbes en J assez respecté, malgré un léger surplus de savoir fragile (70%)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Sur les courbes J, j’ai plus d’erreurs dangereuses et de savoirs fragiles.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>je pense être plutôt réaliste et ne pas avoir besoin de devenir beaucoup plus réaliste</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Je pense donc que pour être plus réaliste, je devrais me faire plus confiance,</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ce test ne m'apporte pas grand-chose, que quelques connaissances sur quelques détails précis</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Pour le prochain test, il faut moins de doutes sur les choses connues.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>['MotOrient.Value']</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Je devrais être plus attentif sur les questions.</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>je devrai plus réfléchir sur les questions et mes connaissances</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>une erreur dangereuse, j'ai eu beaucoup de savoir fragile (6)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>J’ai eu beaucoup de savoirs fragiles (8)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>J'ai appris que je devrais me fier plus à mes connaissances qu'à la pertinence de la question</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>je devrai plus réfléchir sur les questions et mes connaissances</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Résultat : 20/32 , j'ai fait 16 réponses correctes</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>J’ai un résultat de 16/20 dont 3 réponses au hasard.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>un savoir certain , 4 savoir fragile , pour les erreurs, 5 erreur dangereuse et 7 erreur présumée</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Erreur dangereuse : 6 Savoir fragile 5 erreur présumée : 2 Savoir certain 15</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Je repère beaucoup de prudence car je peux présumer mes erreurs éventuel , ce qui me permet d'avoir peut d'erreur dangereuse.</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>J’ai fait preuve de prudence.</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret', 'MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Pour m'améliorer davantage, il faut que je réponde plus spontanément car il y a des questions où j'ai trop hésité</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Pour devenir davantage réaliste, il faudrait que je passe plus de temps pour répondre à la question.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>['CTRL', 'StratKldg']</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>21 réponses correctes, 5 ignorances et 6 réponses incorrectes</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Il y a beaucoup de réponses correctes (14/20) 5 réponses d’ignorance et 1 réponse incorrecte</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ces erreurs dangereuses sont dues à un manque de connaissances.</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Mes erreurs dangereuses sont surtout dues a des petites erreurs d’étourderie.</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>La courbe en J est bien remarquable avec les réponses correctes qui sont croissantes. Par contre, elle n'est pas respectée avec les réponses incorrectes, dû aux erreurs dangereuses</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>La courbe d’erreur ne forme pas un J contrairement à la courbe de bonnes réponses</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>La prochaine fois, je ferais attention aux tournures des phrases qui peuvent être dangereuses.</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>J’ai fait tout de même 5 erreurs dangereuses</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>5 incorrectes, 5 ignorances, 22 correctes -&gt; 24/32</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Mon résultat 30/40 , 8 réponses incorrectes , 5 ignorances , 27 réponses correctes</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Courbe en J similaire pour les réponses correctes mais pas pour les incorrectes (moins exponentielle)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Par rapport aux écarts, ma courbe des réponses correctes forme bien un J mais pas celle des réponses incorrectes.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Plutôt des erreurs d'inattention que du manque de réalisme.</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Des erreurs d’inattention</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>sachant que je n'étais pas là pour la leçon de géométrie moléculaire et que je n'ai pas très bien compris</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>J’étais globalement assez cohérente dans mon degré de certitude et la justesse de mes réponses</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Il y a plus de réponses correctes qu'incorrectes mais il y a aussi pas mal d'ignorances</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Il y a eu plus de réponses correctes que d’erreurs, mais aussi un certain nombre d’ignorances</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Pour les réponses incorrectes, il y a bien une courbe en J, par contre pour les réponses incorrectes la courbe n'a pas cette forme.</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>La courbe d’erreur ne forme pas un J contrairement à la courbe de bonnes réponses</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Il y a pas mal de savoir fragile ce qui montre de la prudence.</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>je suis plutôt prudente, je sais quand mon savoir est certain ou fragile</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Pour le prochain test il faudrait que je fasse preuve de plus de certitude.</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Il faudrait que je révise davantage pour le prochain test</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>quelques difficultés en chimie.</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>quelques réponses faibles.</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>La courbe des réponses correctes ne correspond pas à la courbe en J car il y a beaucoup de savoirs fragiles</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>La courbe de réponses correctes suit presque la courbe en J avec quand même beaucoup de savoir fragile malgré qu’il y en a beaucoup moins que de savoir certain. Cependant la courbe de réponse incorrectes ne suit pas du tout la courbe en pointillés puisqu’il y a beaucoup d’erreurs dangereuses 6 pour 9 réponses incorrect.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Il faudrait qu'au prochain test je sois plus sûr de moi pour avoir moins de savoir fragile et aussi avoir moins d'erreurs dangereuses.</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Lors du prochain test il faudrait diminuer le nombre d’erreurs dangereuses et me rapprocher de la courbe en J et aussi diminuer le savoir fragile afin d’être plus certaine.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>La chimie est vraiment dure, mais la physique c'est bien</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>je ne connaisse pas ma leçon de chimie et que je comprends assez bien la physique.</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Note 22/32-&gt; 10 réponses incorrectes et 22 réponses correctes</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>J’ai eu 28/44, j’ai eu 24 réponses correctes</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>imprudence</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>révèle de l’imprudence</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>donc je suis trop confiante</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Je suis donc trop prudente</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Mes courbes sont loin de celle en J</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Les courbes en J sont plutôt écrasées</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>je suis mi prudente/ mi imprudente.</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Je suis peut-être imprudente</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Lors du prochain test, il faudrait que je prenne plus de temps sur les questions pour réellement réfléchir parce que là j'avais un peu la flemme de réfléchir à 100%. Et passer plus de temps sur les questions où je pense être certaine.</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>je devrai plus réfléchir sur les questions et mes connaissances</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Dans les réponses correctes la courbe J est bien suivie. Par contre du côté des réponses incorrectes il y a plus de réponses dangereuses que présumée</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>La courbe de réponses correctes suit presque la courbe en J avec quand même beaucoup de savoir fragile malgré qu’il y en a beaucoup moins que de savoir certain. Cependant la courbe de réponse incorrectes ne suit pas du tout la courbe en pointillés puisqu’il y a beaucoup d’erreurs dangereuses 6 pour 9 réponses incorrect.</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>ce qui traduit encore une légère imprudence</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>je fais donc preuve d’un peu imprudence.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Pour la prochaine je dois être plus prudente</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Je devrais être plus prudent pour les prochains.</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>il faut revoir certaines choses de mon cours</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>J’ai plutôt pas mal de savoir certain</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>23 savoir certain et pas d'erreur présumée et pas de savoir fragile</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>J’ai 20 savoir certains et 15 savoir fragile</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>On peut penser à une imprudence car mes résultats se trouvent dans les extrêmes.</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Mes résultats d’après les courbes en J révèle de l’imprudence tout de même</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Afin d'être plus réaliste lors du prochain test, une meilleure connaissance de son cours serait préférable</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Je pourrais devenir davantage réaliste lors de prochain test en acquérant (!) plus de connaissance.</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Globalement 24/32 ce n’est pas trop mal pour moi</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Globalement il y a beaucoup de réponses correctes, score globale = 22/28</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Il y a eu quand même 15 savoir certain, 8 savoir fragile</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>J’ai 20 savoir certains et 15 savoir fragile</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Pour les réponses correctes mes résultats correspondent à la courbe en J en général avec un pourcentage un peu trop élevé de savoir fragile.</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Dans les réponses correctes, j’ai beaucoup plus de savoirs certains que de savoir fragile</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Pour devenir davantage réaliste je devrais réfléchir plus longtemps sur certaines questions et faire attention aux pièges.</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>je devrai plus réfléchir sur les questions et mes connaissances</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Erreur dangereuse 4, Erreur présumée 3, savoir certain 24, 1 ignorance déclarée</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>1 erreur dangereuse, 3 erreurs présumées, 3 ignorances déclarées, 3 savoir fragile et 18 savoir certains</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>J'ai eu tout juste en physique, mais j'ai plus de mal en chimie car c'est moins concret. Les formules sont dures à comprendre donc à apprendre. De plus, mes erreurs dangereuses en chimie montrent que je n'ai pas tout compris.</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>J’ai eu beaucoup (~) de erreurs dangereuses mais en tout pas mal de réponse juste</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Ce score global (par rapport aux erreurs dangereuses) est peut-être dût à de la précipitation</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Les erreurs dangereuses en était globalement peut nombreuse mêmes si ce n’est pas encore ça, mais je trouve que j’ai un savoir un peu fragile même si globalement c’est bien.</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC', 'StratKldg']</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>La courbe en J au niveau des réponses incorrectes n'est pas bonne</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>La courbe d’erreur ne forme pas un J contrairement à la courbe de bonnes réponses</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>il y a trop d’assurance pour des réponses qui sont fausses</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>j’ai donc tendance a être trop confiant sur des réponses fausses et pas assez sur des réponses exacts.</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>['MotOrient.SelfEff']</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Je pourrais être plus réaliste en lisant mieux les questions.</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>je devrai plus réfléchir sur les questions et mes connaissances</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Des bonnes connaissances dans certains chapitres et des manques de connaissances notamment pour les ondes et le titrage, ainsi que les représentations des molécules dans l'espace.</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>d’un manque de connaissances sur certains points</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Bon test permettant ainsi de connaitre la qualité des connaissances.</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Globalement, le test m’a donné de la confiance dans mes connaissances</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>['MotOrient.Value']</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>De bonnes connaissances dans certains domaines, comme de sérieuses lacunes dans d'autres.</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>d’un manque de connaissances sur certains points</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>6 erreurs dangereuses, 18 savoirs certains et 4 savoir fragiles, 1 erreur présumée.</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>1 erreur dangereuse, 3 erreurs présumées, 3 ignorances déclarées, 3 savoir fragile et 18 savoir certains</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Les erreurs dangereuses viennent du fait que je lis parfois trop vite et de ce fait j'oublie des informations</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Et un peu trop d’erreurs dangereuses</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>['StratKldg', 'MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>4 erreurs dangereuses et 6 erreurs présumées et 4 savoir fragile ainsi que 18 savoir certain</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>1 erreur dangereuse, 3 erreurs présumées, 3 ignorances déclarées, 3 savoir fragile et 18 savoir certains</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Je suis allée beaucoup trop vite sur certaines questions</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Je pense que certaines questions que je maitrise j’y suis aller trop vite et ai donc commis des erreurs</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>je ne me suis pas fait assez confiance.</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>je ne suis pas assez sûre de moi.</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>['MotOrient.SelfEff']</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Globalement, il y a 23 réponses correctes et 9 réponses incorrectes ce qui est moins bon que la dernière fois.</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Globalement, il y a beaucoup de réponses correctes, (17 sur 24)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Pour les réponses incorrectes, mes résultats vont en descendant en fonction du degré de certitude mais les réponses correctes suivent la courbe en J</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Pour les réponses incorrectes, il y a plus d’erreur à 90% / 80% de certitude et cela ne suit pas la courbe en J. En revanche, pour les réponses correctes, plus la courbe augmente, plus le savoir certain augmente aussi malgré 60% de certitude au début. Mais relativement de faibles écarts entre la courbe en J et résultats</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Cela révèle probablement d'imprudence considérable mais de sureté bénéfique.</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Cela révèle donc de certaines imprudences au niveau du jugement.</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Lors du prochain test, il s'agira de se montrer moins sur à 100% sur des réponses, même pour les réponses où je suis sûr de moi</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Pour être davantage réaliste lors du prochain test, il faudrait lorsqu’une de mes réponses n’est pas certaine à 100%, baisser le pourcentage à 80% ou à 60 % pour être plus prudente.</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>mon jugement n'est pas réaliste</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mon jugement est moyennement réaliste </t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>['MotOrient.SelfEff']</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Je suis donc trop imprudent.</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Je suis donc trop prudente</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Certaines de ces erreurs sont dues à un manque de réflexion par rapport aux questions (ex: confondre semi-équation et équation de réaction)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>C’est quand même intéressant de voir sur quelles questions on a fait une erreur dangereuse car je me suis rendu compte que je faisais quelques erreurs bêtes. *</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>['StratKldg', 'DomKldg']</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Mes fautes sont surtout en chimie, c'est tout à fait normal car je ne comprends pas trop certaines méthodes à faire</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>J’ai fait des erreurs d’inattention, sans vraiment réfléchir à toutes les questions.</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>beaucoup trop d'erreur dangereuses mais une courbe de savoir certain plutôt bonne</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Et un peu trop d’erreurs dangereuses</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC', 'MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Il faut que je travaille mieux mes notions</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Il me faut mieux connaitre mon cours plus tard.</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Résultat de 28/32</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Résultat de 23/28 questions</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>L'objectif est donc une attention plus marquée dans la lecture des questions</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>J’observe une bonne certitude sur une majorité des questions</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Le cours doit être relu et mieux compris. Bonne compréhension pour la réaction d'oxydation, la diffraction et les lois de Newton.</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Il faudrait plus de connaissances pour mieux le réussir.</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Les courbes en J ne sont pas cohérentes, au niveau des réponses incorrectes : bcp de réponses dangereuses à 100% ou 90% de certitude.</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Globalement, il y a quelques erreurs dangereuses (3) et présumées (3) et une majorité de réponses correctes. La courbe ne J atteint son maximum dans les réponses correctes pour 80%.</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>10 réponses correctes sur 20, score correct</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Globalement, mon score est correct (équivaut à 16/20)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>trois erreurs dangereuses (à80%) qui sont dues à une mauvaise lecture de l'énoncé et une confusion entre plusieurs éléments de la consigne</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Globalement, il y a quelques erreurs dangereuses (3) et présumées (3) et une majorité de réponses correctes. La courbe ne J atteint son maximum dans les réponses correctes pour 80%.</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC', 'StratKldg']</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>j'ai 7 savoir certain et 3 savoir fragile,</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>J’ai 20 savoir certains et 15 savoir fragile</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>ce qui témoigne d'une bonne connaissance d'une partie du programme et une connaissance partielle d'une autre partie du programme</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>On peut constater un manque de confiance concernant les connaissances acquises et comprises.</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Pour un meilleur résultat la fois prochaine, il faudrait ouvrir le livre de SPC notamment sur la mécanique</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Il faut donc que je prenne plus de temps pour répondre &amp; lire les questions la prochaine fois.</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>j'ai souvent répondu trop vite</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>je semble encore trop confiant</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>je n'avais pas de connaissance spécifique sur ce cours (mots spécifiques scientifiques)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>il faudrait que je sois bien plus rigoureux sur les connaissances de cours</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>4 erreurs dangereuses, 3 erreurs présumées et 13 savoirs certains</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Résultats : 45 savoirs certains et 3 erreurs dangereuses. 2 erreurs dangereuses</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Pour la prochaine fois, essayer de prendre plus de temps dans la lecture de certaines questions</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Pour la prochaine je pourrais prendre plus mon temps</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Je suis arrivée à un résultat de 12/20</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>J’ai un résultat de 16/20 dont 3 réponses au hasard.</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>j'ai été beaucoup moins prudente que sur le dernier test, j'ai pris des risques</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Même si lors du test, j’ai malheureusement échangé les réponses de certaines questions (donc deux erreurs dangereuses pour rien) et d’autres étaient ambigües.</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Il faut encore que je me concentre davantage sur les énoncés, prendre le temps de bien lire surtout sur la mécanique</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Il faut donc prendre son temps et vérifier même si on est sûr de la réponse.</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>['CTRL']</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>9 savoir certain 4 fragile 4 erreurs présumées et 3 dangereuses.</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>1 erreur dangereuse, 3 erreurs présumées, 3 ignorances déclarées, 3 savoir fragile et 18 savoir certains</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>des confusions et des souvenirs erronés du à des réponses données basées non pas sur un cours appris mais sur des souvenirs de classes et des exercices faits.</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>dû au fait que je confonds des notions de cours</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>mes erreurs viennent majoritairement du fait que je ne comprends absolument pas le chapitre de chimie sur lequel nous avons eu des questions (solution titrante/titrée, ph, pka)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>J’observe une bonne certitude sur une majorité des questions</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>j'ai fait beaucoup d'erreurs présumées</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>j’ai fait beaucoup d’erreurs</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>j'ai échangé 2 valeurs dans une formule que je n'ai pas trop comprise</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dans l’ensemble je suis très voire trop sûr de moi </t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>je n'ai pas bien relu mes chapitres</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Je n’ai pas assez revu certain chapitre.</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>j’ai des fois mal lu les consignes</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>j’ai un manque de connaissances.</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>pour ce second test, j'ai eu 9 réponses correctes, 4 ignorances et 7 réponses incorrectes.</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Globalement j’ai eu plus de réponse correctes (20) malgré 17 réponses incorrects et 3 ignorances.</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Je dois revoir les chapitres de chimie (acido-basique) et également en mécanique, les lois de Kepler et la mécanique des électrons.</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>je ne connaisse pas ma leçon de chimie et que je comprends assez bien la physique.</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>J’aurais mieux réussis si j’avais pu poser les questions à l'écrit sur une feuille et si j'avais pour prendre mon temps en recontextualisant les questions qui ont déjà été vues en classes ou évaluation.</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Pour la plupart des questions, j’ai plutôt bien réussi à dire si j’allais avoir juste ou non</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>['StratKldg', 'CTRL']</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>je pense que le cours est moins maitrisé</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>ce sont les chapitres que je maitrisais moins.</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>je n'ai pas pris le temps de bien comprendre les énoncés</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Pour la prochaine je pourrais prendre plus mon temps</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>J'ai quand même pu corriger le problème du premier test sur le fait que je n'avais pas confiance en moi</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>c’est un gros problème que j’ai depuis très longtemps ! Je voudrais donc finir par dire merci pour ce test, c’était un bon boost de confiance ! :)</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>['MotOrient.SelfEff', 'StratKldg']</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>dans certaines questions je n’étais pas concentré sur le sujet</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Je pense ne pas être assez sûr de moi pour certaines questions</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Incompréhension acide/base + titrage</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Réponses incorrectes : 4ignorances : 7réponses correctes</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>J'ai obtenu 10 réponses correctes et 9 réponses incorrectes avec une ignorance déclarée</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Globalement, il y a beaucoup de réponses correctes (31), peu de réponses incorrectes (9) et aucune ignorance</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>j'ai été plus réaliste</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Je pourrais être plus réaliste en révisant plus et en me précipitant moins</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Il y a 8 savoir certain et deux savoir fragile</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>J’ai 20 savoir certains et 15 savoir fragile</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>mes connaissances pas encore assez solides.</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>je n’étais pas sûr de mes connaissances sur certaines réponses.</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>['MonCal.Interpret']</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Ceci démontre de mon évolution sur le plan mental notamment. Dans mon assurance à répondre aux questions.</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>J’ai fait des erreurs d’inattention, sans vraiment réfléchir à toutes les questions.</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>['MotOrient.SelfEff']</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>mon problème réside dans ma précipitation</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>J’espère devenir réaliste en prenant plus mon temps</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>J'ai eu 9 réponses incorrectes</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>J’ai eu beaucoup de réponses correctes, seulement 2 incorrectes.</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.RF']</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>4 dangereuses et 5 présumées</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Résultats : 45 savoirs certains et 3 erreurs dangereuses. 2 erreurs dangereuses</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>J'ai répondu trop vite aux questions. je n'ai pas assez réfléchi à certaines questions.</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>je devrai plus réfléchir sur les questions et mes connaissances</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>j'ai pas revu le cours</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Je n’ai pas assez revu certain chapitre.</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>je suis allé trop vite et du coup mauvaise lecture/compréhension</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>certaines erreurs dû à de l’inattention ou à la vitesse de lecture (trop vite)</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>un manque d'attention sur certains détails</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>d’un manque de connaissances sur certains points</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>une confusion dans mes connaissances</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Mes connaissances insuffisantes</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Des erreurs que je pouvait éviter souvent dû au manque de concentration</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>on peut penser que je suis assez prudent</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>il faut que je révise les formules de Kepler et revoir les charges électriques</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>réviser avant, analyser les réponses dangereuses. Ne pas avoir la flemme de faire les calculs.</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>['DomKldg', 'CTRL']</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Chapitres pas assez bien travaillés</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Je n’ai certainement pas assez travaillé</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>5 dangereuses, 2 présumées, 1 ignorance , 4 fragiles, 8 certains</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>32 savoirs certains, 2 savoirs fragiles, 7 erreurs présumées, 4 erreurs dangereuses, 3 ignorance déclarée-</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>mauvais apprentissage du cours</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>en apprenant mieux en cours,</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>bcp d'erreurs dangereuses</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Cependant trop d’erreurs dangereuses (7/40)</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>['MonCal.Facts.DC']</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
           <t>bien relire les consignes</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C235" t="inlineStr">
         <is>
           <t>Il faudrait plus de connaissances pour mieux le réussir.</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>DomKldg</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>['StratKldg']</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
         <is>
           <t>StratKldg</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>StratKldg</t>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Difficultés dans le chapitre sur la loi de Newton</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Manque de connaissance sur certains chapitres</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>['DomKldg']</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
         </is>
       </c>
     </row>
